--- a/labs/lab-4/downloads/Lab_4_Tone_Evaluation_and_Version_Scorecard.xlsx
+++ b/labs/lab-4/downloads/Lab_4_Tone_Evaluation_and_Version_Scorecard.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R9121f661cf45483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output Scores" sheetId="2" r:id="Ra4d8ca33fdac497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule Review" sheetId="3" r:id="R7c5c167186f745e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Requests" sheetId="4" r:id="Re73961812d064297"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tone Versions" sheetId="5" r:id="R446ffce4e55e401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Before After" sheetId="6" r:id="Rab0506b1c03c4c54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R68ba82df22d74cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output Scores" sheetId="2" r:id="R09c2281b182e43f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule Review" sheetId="3" r:id="Rf8a8d90c7c294898"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Requests" sheetId="4" r:id="R8c4545a0873f44df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tone Versions" sheetId="5" r:id="R0ad819ac5e334b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Before After" sheetId="6" r:id="Ra1ed8c669bb34c42"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -791,7 +791,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="40" t="str">
-        <x:v>Paste exact before-and-after sentences into Before After and confirm what stayed unchanged.</x:v>
+        <x:v>Ask Copilot in Excel Edit mode to write exact before-and-after sentences into Before After; review before Apply.</x:v>
       </x:c>
       <x:c r="C11" s="38"/>
       <x:c r="D11" s="38"/>
@@ -1007,7 +1007,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="35" t="str">
-        <x:v>Enter scores from 1 to 5. Unsupported additions are a count and automatically trigger Reject.</x:v>
+        <x:v>Use Copilot in Excel Edit mode to add drafts and scores. Review target rows before Apply; unsupported additions trigger Reject.</x:v>
       </x:c>
       <x:c r="B2" s="36"/>
       <x:c r="C2" s="36"/>
@@ -1974,7 +1974,7 @@
         <x:v>Initial profile</x:v>
       </x:c>
       <x:c r="E5" s="40" t="str">
-        <x:v>Paste the complete approved v1.0 instruction or link to the approved Tone Profile document.</x:v>
+        <x:v>Ask Copilot in Excel Edit mode to write the complete approved instruction or controlled Tone Profile reference.</x:v>
       </x:c>
       <x:c r="F5" s="40" t="str"/>
       <x:c r="G5" s="40" t="str"/>
@@ -1994,7 +1994,7 @@
         <x:v>Opening and closing warmth for existing clients</x:v>
       </x:c>
       <x:c r="E6" s="40" t="str">
-        <x:v>Paste the complete v1.1 instruction after TCR-001 is approved.</x:v>
+        <x:v>Ask Copilot in Excel Edit mode to write v1.1 after TCR-001 is approved.</x:v>
       </x:c>
       <x:c r="F6" s="40" t="str"/>
       <x:c r="G6" s="40" t="str">
@@ -2204,7 +2204,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="35" t="str">
-        <x:v>Paste exact sentences and show what changed, why it changed and what remained fixed.</x:v>
+        <x:v>Use Copilot in Excel Edit mode to write exact sentences and show what changed, why it changed and what remained fixed.</x:v>
       </x:c>
       <x:c r="B2" s="36"/>
       <x:c r="C2" s="36"/>
